--- a/stats for com eng/Ch3-02.xlsx
+++ b/stats for com eng/Ch3-02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pin/Desktop/joint-repository/stats for com eng/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pinpin\Desktop\joint-repository\stats for com eng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219310BA-4748-4444-A53F-D9636AD8AE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3D6207-2756-4B46-A85F-3694D81885AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="24080" windowHeight="13220" activeTab="1" xr2:uid="{8DEBBECD-A99A-49B1-B4B6-AB7841D25FAA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{8DEBBECD-A99A-49B1-B4B6-AB7841D25FAA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t xml:space="preserve">P(Z &gt; 1.26) = </t>
   </si>
@@ -179,6 +179,12 @@
   </si>
   <si>
     <t>( X - mean ) / standard div</t>
+  </si>
+  <si>
+    <t>1-0.99 = 0.01</t>
+  </si>
+  <si>
+    <t>z=2.58</t>
   </si>
 </sst>
 </file>
@@ -282,7 +288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -315,6 +321,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -630,19 +639,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC33ED9-CF7B-4298-9EF7-3D67594E1569}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.6640625" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -653,7 +662,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
@@ -665,7 +674,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>28</v>
       </c>
@@ -681,7 +690,7 @@
         <v>0.10025884372280375</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D5" s="14">
         <v>1</v>
       </c>
@@ -690,7 +699,7 @@
         <v>0.23059534056244857</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D6" s="14">
         <v>2</v>
       </c>
@@ -699,7 +708,7 @@
         <v>0.26518464164681593</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D7" s="14">
         <v>3</v>
       </c>
@@ -708,7 +717,7 @@
         <v>0.20330822526255887</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D8" s="14">
         <v>4</v>
       </c>
@@ -717,7 +726,7 @@
         <v>0.11690222952597135</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D9" s="14">
         <v>5</v>
       </c>
@@ -726,7 +735,7 @@
         <v>5.377502558194678E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
         <v>29</v>
       </c>
@@ -735,12 +744,12 @@
         <v>0.97002430630254521</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>25</v>
       </c>
@@ -755,7 +764,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>32</v>
       </c>
@@ -764,12 +773,12 @@
         <v>0.11293507088124352</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>25</v>
       </c>
@@ -784,7 +793,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
         <v>33</v>
       </c>
@@ -801,21 +810,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6217950-0915-478B-BD30-79A941DA3306}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="7" customWidth="1"/>
-    <col min="4" max="6" width="8.6640625" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="8.6640625" style="7"/>
+    <col min="1" max="1" width="20.6328125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="10.6328125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="10.6328125" style="7" customWidth="1"/>
+    <col min="4" max="6" width="8.6328125" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="8.6328125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>19</v>
       </c>
@@ -826,7 +835,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -842,7 +851,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -852,7 +861,7 @@
       </c>
       <c r="C4" s="9"/>
     </row>
-    <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
@@ -861,15 +870,15 @@
         <v>0.68268949213708607</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C7" s="9"/>
     </row>
-    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -884,7 +893,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -896,11 +905,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="7"/>
       <c r="C11" s="9"/>
     </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>15</v>
       </c>
@@ -911,7 +920,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>12</v>
       </c>
@@ -919,7 +928,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -929,7 +938,7 @@
       </c>
       <c r="C14" s="9"/>
     </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -939,7 +948,7 @@
       </c>
       <c r="C15" s="9"/>
     </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
@@ -949,7 +958,7 @@
       </c>
       <c r="C16" s="9"/>
     </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>16</v>
       </c>
@@ -961,7 +970,7 @@
         <v>2.0537489106318221</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>17</v>
       </c>
@@ -973,7 +982,7 @@
         <v>14.107497821263644</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -983,7 +992,7 @@
       </c>
       <c r="C21" s="9"/>
     </row>
-    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>18</v>
       </c>
@@ -1001,54 +1010,80 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF4B88EE-10A4-452A-84F0-3D55D1ADE700}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="30.6328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6328125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-    </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="4">
+        <f>1-_xlfn.NORM.S.DIST(1.26, TRUE)</f>
+        <v>0.10383468112130034</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
     </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4"/>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="4">
+        <f>_xlfn.NORM.S.DIST(0.37, TRUE) - _xlfn.NORM.S.DIST(-1.25, TRUE)</f>
+        <v>0.53865898113369159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4"/>
-    </row>
-    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="4">
+        <f>_xlfn.NORM.S.DIST(-4.6, TRUE)</f>
+        <v>2.1124547025028533E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="B6" s="4">
+        <f>_xlfn.NORM.S.INV(0.05)</f>
+        <v>-1.6448536269514726</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="20" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="2">
+        <f>_xlfn.NORM.S.INV(0.995)</f>
+        <v>2.5758293035488999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
